--- a/drone/droneMemo.xlsx
+++ b/drone/droneMemo.xlsx
@@ -5,14 +5,15 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sou\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\Arduino Uno\esp32Arduino\drone\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15220" windowHeight="8460"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15220" windowHeight="8460" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <r>
       <t xml:space="preserve">2N2222 是一种常用的 </t>
@@ -427,6 +428,9 @@
       </rPr>
       <t>。 [6, 7, 15, 16, 17, 18, 19, 20]</t>
     </r>
+  </si>
+  <si>
+    <t>https://elchika.com/article/38a20e84-7776-4c12-9836-255a789bf206/</t>
   </si>
 </sst>
 </file>
@@ -569,6 +573,121 @@
         <a:xfrm>
           <a:off x="336550" y="3968750"/>
           <a:ext cx="9753600" cy="5010150"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="キャプションを入力できます"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="330200"/>
+          <a:ext cx="6096000" cy="4572000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2" descr="キャプションを入力できます"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="5118100"/>
+          <a:ext cx="6096000" cy="4572000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -941,4 +1060,21 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>